--- a/Tables/Data/__enums__.xlsx
+++ b/Tables/Data/__enums__.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -763,6 +763,86 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Skin</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>皮</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>皮：身份的载体之一，也可作合成原料</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>面具</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>面具：身份的载体之一</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>钥匙</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>钥匙：一次性或持有时用来开某扇门 / 过某个关口</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>文书</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>文书：可翻页阅读的簿册</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
